--- a/sales.xlsx
+++ b/sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amplifon-my.sharepoint.com/personal/gautham_menon_amplifon_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF2FD0DB-CBA5-43FE-9CEA-9E19BC4D2417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{EF2FD0DB-CBA5-43FE-9CEA-9E19BC4D2417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FA963F3-6A80-45C6-AECF-CE17A3683C95}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4558D6B1-A4AF-4EE8-A597-41D9B76A9519}"/>
   </bookViews>
@@ -39,9 +39,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>CustomerID</t>
+  </si>
+  <si>
+    <t>CustomerID2</t>
+  </si>
+  <si>
+    <t>CustomerID3</t>
   </si>
 </sst>
 </file>
@@ -453,29 +459,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{353CED43-FA7E-4022-8472-6BDB53C6BA98}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1001</v>
       </c>
+      <c r="B2" s="2">
+        <v>1001</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1001</v>
+      </c>
     </row>
-    <row r="3" spans="1:1" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>1002</v>
       </c>
+      <c r="B3" s="2">
+        <v>1002</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1002</v>
+      </c>
     </row>
-    <row r="4" spans="1:1" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1003</v>
+      </c>
+      <c r="C4" s="2">
         <v>1003</v>
       </c>
     </row>
